--- a/DATA/MODELADO/Modelos/Exp04/registro_Exp04.xlsx
+++ b/DATA/MODELADO/Modelos/Exp04/registro_Exp04.xlsx
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46234.06075361478</v>
+        <v>46234.10205650901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -672,60 +672,48 @@
         <v>100</v>
       </c>
       <c r="R2" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="S2" t="n">
-        <v>0.008079231716692448</v>
+        <v>0.00463638361543417</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03858808055520058</v>
+        <v>0.03598886355757713</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06700899451971054</v>
+        <v>0.07414160668849945</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05952026695013046</v>
+        <v>0.04165492206811905</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1653102338314056</v>
+        <v>0.1639291346073151</v>
       </c>
       <c r="X2" t="n">
-        <v>0.08988454937934875</v>
+        <v>0.06809099763631821</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1964384913444519</v>
+        <v>0.1897073090076447</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2191405594348907</v>
+        <v>0.2453693002462387</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2588609457015991</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.9487179487179487</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.8181818181818181</v>
-      </c>
+        <v>0.2722895741462708</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>MODELO APROBADO</t>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>10.65025329589844</v>
+        <v>24.39480328559875</v>
       </c>
     </row>
   </sheetData>
